--- a/notebooks/evaluation_results/results_distribution_metrics.xlsx
+++ b/notebooks/evaluation_results/results_distribution_metrics.xlsx
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7924376144126801</v>
+        <v>0.7539763253868697</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2777129521586931</v>
+        <v>0.3514644351464435</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5613120707717665</v>
+        <v>0.4694825122873099</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.965877395859332</v>
+        <v>0.9333986548012576</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04492415402567095</v>
+        <v>0.104602510460251</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08446250402142513</v>
+        <v>0.1622353843844646</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9106290421903197</v>
+        <v>0.9246189261553701</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1161026837806301</v>
+        <v>0.08786610878661087</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2310146933318488</v>
+        <v>0.1111542211451169</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9512086773657015</v>
+        <v>0.9024229508305996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0647607934655776</v>
+        <v>0.1380753138075314</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1224132902233958</v>
+        <v>0.2179568037014099</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9529703320457493</v>
+        <v>0.9621480665203033</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06359393232205368</v>
+        <v>0.05857740585774059</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1208086103793857</v>
+        <v>0.09495130993476925</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9512086773657015</v>
+        <v>0.9024229508305996</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0647607934655776</v>
+        <v>0.1380753138075314</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1224132902233958</v>
+        <v>0.2179568037014099</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9547316128058768</v>
+        <v>0.908282940400269</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06067677946324387</v>
+        <v>0.1297071129707113</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1149876755522268</v>
+        <v>0.1965708762430945</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9612684264754643</v>
+        <v>0.9127440347676745</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05134189031505251</v>
+        <v>0.1255230125523012</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1009791812072978</v>
+        <v>0.1797909720309352</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9637765759366966</v>
+        <v>0.9444909546249094</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04900816802800467</v>
+        <v>0.08368200836820083</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0942676470456117</v>
+        <v>0.1320599833162335</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9628772376909372</v>
+        <v>0.9497973681158103</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04842473745624271</v>
+        <v>0.07531380753138076</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07787738562085042</v>
+        <v>0.1031122191295016</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9528134289114957</v>
+        <v>0.9024248013516061</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06301050175029171</v>
+        <v>0.1380753138075314</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1189648562545798</v>
+        <v>0.2172943786537884</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
